--- a/PIPELINE 2026-2027.xlsx
+++ b/PIPELINE 2026-2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vrodriguez\Desktop\Directorio J\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5637C4B-2103-46C3-8BB6-7709AB9063A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0158FB-09FD-4C9F-9761-E3E9C9B96884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00A14261-C0D4-4AD8-9D5C-73D2E7CCEB70}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="223">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -724,6 +724,9 @@
   </si>
   <si>
     <t>VENTA</t>
+  </si>
+  <si>
+    <t>Vendido</t>
   </si>
 </sst>
 </file>
@@ -1889,7 +1892,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -1971,7 +1974,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>52</v>
       </c>
@@ -2012,7 +2015,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>55</v>
       </c>
@@ -2215,7 +2218,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>67</v>
       </c>
@@ -2256,7 +2259,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>71</v>
       </c>
@@ -2377,7 +2380,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>77</v>
       </c>
@@ -2459,7 +2462,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>80</v>
       </c>
@@ -2500,7 +2503,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>82</v>
       </c>
@@ -2623,7 +2626,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>87</v>
       </c>
@@ -2664,7 +2667,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>89</v>
       </c>
@@ -2785,7 +2788,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>96</v>
       </c>
@@ -2867,7 +2870,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>100</v>
       </c>
@@ -2906,7 +2909,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>103</v>
       </c>
@@ -2945,7 +2948,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>105</v>
       </c>
@@ -3027,7 +3030,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>60</v>
       </c>
@@ -3107,7 +3110,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>113</v>
       </c>
@@ -3269,7 +3272,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>122</v>
       </c>
@@ -3357,10 +3360,10 @@
         <v>127</v>
       </c>
       <c r="C46" s="5">
-        <v>657241.41</v>
+        <v>611603.23</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>69</v>
+        <v>222</v>
       </c>
       <c r="E46" s="32" t="s">
         <v>15</v>
@@ -3390,7 +3393,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>128</v>
       </c>
@@ -3431,7 +3434,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>130</v>
       </c>
@@ -3511,7 +3514,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>134</v>
       </c>
@@ -3552,7 +3555,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>136</v>
       </c>
@@ -3593,7 +3596,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>136</v>
       </c>
@@ -3634,7 +3637,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>136</v>
       </c>
@@ -3837,7 +3840,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>148</v>
       </c>
@@ -3878,7 +3881,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>150</v>
       </c>
@@ -3919,7 +3922,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>152</v>
       </c>
@@ -4001,7 +4004,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>156</v>
       </c>
@@ -4042,7 +4045,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>159</v>
       </c>
@@ -4124,7 +4127,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>163</v>
       </c>
@@ -4206,7 +4209,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>167</v>
       </c>
@@ -4247,7 +4250,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>169</v>
       </c>
@@ -4288,7 +4291,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>171</v>
       </c>
@@ -4327,7 +4330,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>173</v>
       </c>
@@ -4368,7 +4371,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>177</v>
       </c>
@@ -4409,7 +4412,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>107</v>
       </c>
@@ -4491,7 +4494,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>182</v>
       </c>
@@ -4532,7 +4535,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>67</v>
       </c>
@@ -4614,7 +4617,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>188</v>
       </c>
@@ -4696,7 +4699,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>130</v>
       </c>
@@ -4819,7 +4822,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>12</v>
       </c>
@@ -4860,7 +4863,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>197</v>
       </c>
@@ -4899,7 +4902,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>141</v>
       </c>
@@ -4940,7 +4943,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>200</v>
       </c>
@@ -4981,7 +4984,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>202</v>
       </c>
@@ -5022,7 +5025,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>205</v>
       </c>
@@ -5063,7 +5066,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>205</v>
       </c>
@@ -5104,7 +5107,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>205</v>
       </c>
@@ -5145,7 +5148,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>209</v>
       </c>
@@ -5186,7 +5189,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="18" t="s">
         <v>211</v>
       </c>
@@ -5227,7 +5230,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="18" t="s">
         <v>156</v>
       </c>
@@ -5268,7 +5271,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="18" t="s">
         <v>213</v>
       </c>
@@ -5307,7 +5310,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="18" t="s">
         <v>171</v>
       </c>
@@ -5348,7 +5351,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="25" t="s">
         <v>217</v>
       </c>
@@ -5391,6 +5394,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M95" xr:uid="{C6817A9D-27B5-4EE5-98A5-0CA4F5163512}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="AIB MOTUPE"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="12">
       <filters>
         <filter val="2026"/>
